--- a/branches/main/ValueSet-mii-vs-icu-code-monitoring-und-vitaldaten-snomed.xlsx
+++ b/branches/main/ValueSet-mii-vs-icu-code-monitoring-und-vitaldaten-snomed.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="114">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.3</t>
+    <t>2027.0.0-ballot.3-rc.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -159,13 +159,13 @@
     <t>276900001</t>
   </si>
   <si>
-    <t>Systemic vascular Resistance index (observable entity)</t>
+    <t>Systemic vascular resistance index (observable entity)</t>
   </si>
   <si>
     <t>276902009</t>
   </si>
   <si>
-    <t>Pulmonary vascular Resistance index (observable entity)</t>
+    <t>Pulmonary vascular resistance index (observable entity)</t>
   </si>
   <si>
     <t>90096001</t>
@@ -208,6 +208,12 @@
   </si>
   <si>
     <t>Body height (observable entity)</t>
+  </si>
+  <si>
+    <t>1149101003</t>
+  </si>
+  <si>
+    <t>Recumbent body height (observable entity)</t>
   </si>
   <si>
     <t>1153605006</t>
@@ -612,7 +618,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -952,15 +958,23 @@
         <v>109</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>111</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
